--- a/configs/Datas/#CombatConst.xlsx
+++ b/configs/Datas/#CombatConst.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82de574368024c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf6e97483da794f0e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -395,7 +395,7 @@
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E5" s="1" t="str">
-        <x:v>115</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>1</x:v>
@@ -422,7 +422,7 @@
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E6" s="1" t="str">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F6" s="1" t="str">
         <x:v>10</x:v>
@@ -449,7 +449,7 @@
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E7" s="1" t="str">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="1" t="str">
         <x:v>1</x:v>
@@ -476,7 +476,7 @@
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E8" s="1" t="str">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F8" s="1" t="str">
         <x:v>1</x:v>
@@ -521,43 +521,43 @@
     <x:row r="10">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="str">
-        <x:v>ForceExecuteThreshold</x:v>
+        <x:v>MinPickupTime</x:v>
       </x:c>
       <x:c r="C10" s="1" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Clamp</x:v>
       </x:c>
       <x:c r="D10" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E10" s="1" t="str">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="1" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="1" t="str">
-        <x:v>60</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H10" s="1" t="str">
         <x:v>s</x:v>
       </x:c>
       <x:c r="I10" s="1" t="str">
-        <x:v>Low-time execute threshold.</x:v>
+        <x:v>Minimum bomb pickup time.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="str">
-        <x:v>MaxDecisionCount</x:v>
+        <x:v>MaxPickupTime</x:v>
       </x:c>
       <x:c r="C11" s="1" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Clamp</x:v>
       </x:c>
       <x:c r="D11" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E11" s="1" t="str">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F11" s="1" t="str">
         <x:v>1</x:v>
@@ -566,286 +566,286 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H11" s="1" t="str">
-        <x:v>count</x:v>
+        <x:v>s</x:v>
       </x:c>
       <x:c r="I11" s="1" t="str">
-        <x:v>Maximum round decisions.</x:v>
+        <x:v>Maximum bomb pickup time.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="str">
-        <x:v>MaxEncounterPulses</x:v>
+        <x:v>ForceExecuteThreshold</x:v>
       </x:c>
       <x:c r="C12" s="1" t="str">
-        <x:v>Combat</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D12" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E12" s="1" t="str">
-        <x:v>3</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F12" s="1" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="1" t="str">
-        <x:v>8</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H12" s="1" t="str">
-        <x:v>count</x:v>
+        <x:v>s</x:v>
       </x:c>
       <x:c r="I12" s="1" t="str">
-        <x:v>Maximum encounter pulses.</x:v>
+        <x:v>Low-time execute threshold.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1" t="str">
-        <x:v>CombatScale</x:v>
+        <x:v>DecisionDelay</x:v>
       </x:c>
       <x:c r="C13" s="1" t="str">
-        <x:v>Combat</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D13" s="1" t="str">
-        <x:v>Float</x:v>
+        <x:v>Int</x:v>
       </x:c>
       <x:c r="E13" s="1" t="str">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F13" s="1" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="1" t="str">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H13" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>s</x:v>
       </x:c>
       <x:c r="I13" s="1" t="str">
-        <x:v>Combat score scale.</x:v>
+        <x:v>Discrete decision delay.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1" t="str">
-        <x:v>BaseNoise</x:v>
+        <x:v>MaxDecisionCount</x:v>
       </x:c>
       <x:c r="C14" s="1" t="str">
         <x:v>Decision</x:v>
       </x:c>
       <x:c r="D14" s="1" t="str">
-        <x:v>Float</x:v>
+        <x:v>Int</x:v>
       </x:c>
       <x:c r="E14" s="1" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F14" s="1" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="1" t="str">
         <x:v>20</x:v>
       </x:c>
       <x:c r="H14" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>count</x:v>
       </x:c>
       <x:c r="I14" s="1" t="str">
-        <x:v>Base random noise.</x:v>
+        <x:v>Maximum round decisions.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1" t="str">
-        <x:v>MaxRandomNoise</x:v>
+        <x:v>MaxEncounterPulses</x:v>
       </x:c>
       <x:c r="C15" s="1" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Combat</x:v>
       </x:c>
       <x:c r="D15" s="1" t="str">
-        <x:v>Float</x:v>
+        <x:v>Int</x:v>
       </x:c>
       <x:c r="E15" s="1" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F15" s="1" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="str">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="H15" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>count</x:v>
       </x:c>
       <x:c r="I15" s="1" t="str">
-        <x:v>Maximum bounded random noise.</x:v>
+        <x:v>Maximum encounter pulses.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1" t="str">
-        <x:v>CloseScoreGap</x:v>
+        <x:v>MinCombatDuration</x:v>
       </x:c>
       <x:c r="C16" s="1" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Combat</x:v>
       </x:c>
       <x:c r="D16" s="1" t="str">
-        <x:v>Float</x:v>
+        <x:v>Int</x:v>
       </x:c>
       <x:c r="E16" s="1" t="str">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F16" s="1" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="1" t="str">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H16" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>s</x:v>
       </x:c>
       <x:c r="I16" s="1" t="str">
-        <x:v>Close score gap threshold.</x:v>
+        <x:v>Minimum encounter duration.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1" t="str">
-        <x:v>DecisiveScoreGap</x:v>
+        <x:v>MaxCombatDuration</x:v>
       </x:c>
       <x:c r="C17" s="1" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Combat</x:v>
       </x:c>
       <x:c r="D17" s="1" t="str">
-        <x:v>Float</x:v>
+        <x:v>Int</x:v>
       </x:c>
       <x:c r="E17" s="1" t="str">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F17" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G17" s="1" t="str">
-        <x:v>60</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H17" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>s</x:v>
       </x:c>
       <x:c r="I17" s="1" t="str">
-        <x:v>Decisive score gap threshold.</x:v>
+        <x:v>Maximum encounter duration.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1" t="str">
-        <x:v>StrategyRepeatWindow</x:v>
+        <x:v>PulseFireWindow</x:v>
       </x:c>
       <x:c r="C18" s="1" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Combat</x:v>
       </x:c>
       <x:c r="D18" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E18" s="1" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F18" s="1" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="str">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="H18" s="1" t="str">
-        <x:v>round</x:v>
+        <x:v>s</x:v>
       </x:c>
       <x:c r="I18" s="1" t="str">
-        <x:v>Strategy memory window.</x:v>
+        <x:v>Combat pulse fire window.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="1"/>
       <x:c r="B19" s="1" t="str">
-        <x:v>RepeatFreeCount</x:v>
+        <x:v>CombatScale</x:v>
       </x:c>
       <x:c r="C19" s="1" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Combat</x:v>
       </x:c>
       <x:c r="D19" s="1" t="str">
-        <x:v>Int</x:v>
+        <x:v>Float</x:v>
       </x:c>
       <x:c r="E19" s="1" t="str">
-        <x:v>2</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F19" s="1" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="1" t="str">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H19" s="1" t="str">
-        <x:v>round</x:v>
+        <x:v>score</x:v>
       </x:c>
       <x:c r="I19" s="1" t="str">
-        <x:v>Repeat count before penalty.</x:v>
+        <x:v>Combat score scale.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="1"/>
       <x:c r="B20" s="1" t="str">
-        <x:v>StrategyRepeatPenalty</x:v>
+        <x:v>MinDamagePotential</x:v>
       </x:c>
       <x:c r="C20" s="1" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Clamp</x:v>
       </x:c>
       <x:c r="D20" s="1" t="str">
         <x:v>Float</x:v>
       </x:c>
       <x:c r="E20" s="1" t="str">
-        <x:v>3</x:v>
+        <x:v>0.20</x:v>
       </x:c>
       <x:c r="F20" s="1" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G20" s="1" t="str">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H20" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>percent</x:v>
       </x:c>
       <x:c r="I20" s="1" t="str">
-        <x:v>Repeat strategy penalty.</x:v>
+        <x:v>Minimum damage potential.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="1"/>
       <x:c r="B21" s="1" t="str">
-        <x:v>SuccessBonusPerRound</x:v>
+        <x:v>MaxDamagePotential</x:v>
       </x:c>
       <x:c r="C21" s="1" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Clamp</x:v>
       </x:c>
       <x:c r="D21" s="1" t="str">
         <x:v>Float</x:v>
       </x:c>
       <x:c r="E21" s="1" t="str">
-        <x:v>1.5</x:v>
+        <x:v>1.20</x:v>
       </x:c>
       <x:c r="F21" s="1" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G21" s="1" t="str">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H21" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>percent</x:v>
       </x:c>
       <x:c r="I21" s="1" t="str">
-        <x:v>Recent success bonus.</x:v>
+        <x:v>Maximum damage potential.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="1"/>
       <x:c r="B22" s="1" t="str">
-        <x:v>MaxPreviousSuccessBonus</x:v>
+        <x:v>MinExposureModifier</x:v>
       </x:c>
       <x:c r="C22" s="1" t="str">
         <x:v>Clamp</x:v>
@@ -854,376 +854,368 @@
         <x:v>Float</x:v>
       </x:c>
       <x:c r="E22" s="1" t="str">
-        <x:v>6</x:v>
+        <x:v>0.50</x:v>
       </x:c>
       <x:c r="F22" s="1" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G22" s="1" t="str">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H22" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>percent</x:v>
       </x:c>
       <x:c r="I22" s="1" t="str">
-        <x:v>Maximum previous success bonus.</x:v>
+        <x:v>Minimum exposure modifier.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="1"/>
       <x:c r="B23" s="1" t="str">
-        <x:v>CounterMemoryBonus</x:v>
+        <x:v>MaxExposureModifier</x:v>
       </x:c>
       <x:c r="C23" s="1" t="str">
-        <x:v>Decision</x:v>
+        <x:v>Clamp</x:v>
       </x:c>
       <x:c r="D23" s="1" t="str">
         <x:v>Float</x:v>
       </x:c>
       <x:c r="E23" s="1" t="str">
+        <x:v>1.50</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F23" s="1" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="str">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="H23" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>percent</x:v>
       </x:c>
       <x:c r="I23" s="1" t="str">
-        <x:v>Counter memory bonus.</x:v>
+        <x:v>Maximum exposure modifier.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="1"/>
       <x:c r="B24" s="1" t="str">
-        <x:v>MinStrategyWeight</x:v>
+        <x:v>BaseNoise</x:v>
       </x:c>
       <x:c r="C24" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D24" s="1" t="str">
         <x:v>Float</x:v>
       </x:c>
       <x:c r="E24" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F24" s="1" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G24" s="1" t="str">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H24" s="1" t="str">
         <x:v>score</x:v>
       </x:c>
       <x:c r="I24" s="1" t="str">
-        <x:v>Minimum strategy candidate weight.</x:v>
+        <x:v>Base random noise.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="1"/>
       <x:c r="B25" s="1" t="str">
-        <x:v>MaxStrategyWeight</x:v>
+        <x:v>MaxRandomNoise</x:v>
       </x:c>
       <x:c r="C25" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D25" s="1" t="str">
         <x:v>Float</x:v>
       </x:c>
       <x:c r="E25" s="1" t="str">
-        <x:v>100</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F25" s="1" t="str">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G25" s="1" t="str">
-        <x:v>200</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H25" s="1" t="str">
         <x:v>score</x:v>
       </x:c>
       <x:c r="I25" s="1" t="str">
-        <x:v>Maximum strategy candidate weight.</x:v>
+        <x:v>Maximum bounded random noise.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="1"/>
       <x:c r="B26" s="1" t="str">
-        <x:v>ControlIntelTTL</x:v>
+        <x:v>CloseScoreGap</x:v>
       </x:c>
       <x:c r="C26" s="1" t="str">
-        <x:v>Intel</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D26" s="1" t="str">
-        <x:v>Int</x:v>
+        <x:v>Float</x:v>
       </x:c>
       <x:c r="E26" s="1" t="str">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F26" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G26" s="1" t="str">
-        <x:v>60</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H26" s="1" t="str">
-        <x:v>s</x:v>
+        <x:v>score</x:v>
       </x:c>
       <x:c r="I26" s="1" t="str">
-        <x:v>Control intel TTL.</x:v>
+        <x:v>Close score gap threshold.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="1"/>
       <x:c r="B27" s="1" t="str">
-        <x:v>MinAttribute</x:v>
+        <x:v>DecisiveScoreGap</x:v>
       </x:c>
       <x:c r="C27" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D27" s="1" t="str">
-        <x:v>Int</x:v>
+        <x:v>Float</x:v>
       </x:c>
       <x:c r="E27" s="1" t="str">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F27" s="1" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="1" t="str">
-        <x:v>100</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H27" s="1" t="str">
         <x:v>score</x:v>
       </x:c>
       <x:c r="I27" s="1" t="str">
-        <x:v>Minimum attribute value.</x:v>
+        <x:v>Decisive score gap threshold.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="1"/>
       <x:c r="B28" s="1" t="str">
-        <x:v>MaxAttribute</x:v>
+        <x:v>DefaultStrategyTemplateID</x:v>
       </x:c>
       <x:c r="C28" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D28" s="1" t="str">
-        <x:v>Int</x:v>
+        <x:v>String</x:v>
       </x:c>
       <x:c r="E28" s="1" t="str">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="str">
-        <x:v>100</x:v>
-      </x:c>
+        <x:v>Default_Pick</x:v>
+      </x:c>
+      <x:c r="F28" s="1"/>
+      <x:c r="G28" s="1"/>
       <x:c r="H28" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>none</x:v>
       </x:c>
       <x:c r="I28" s="1" t="str">
-        <x:v>Maximum attribute value.</x:v>
+        <x:v>Configured T fallback template.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="1"/>
       <x:c r="B29" s="1" t="str">
-        <x:v>MinHP</x:v>
+        <x:v>DefaultCTSetupTemplateID</x:v>
       </x:c>
       <x:c r="C29" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D29" s="1" t="str">
-        <x:v>Int</x:v>
+        <x:v>String</x:v>
       </x:c>
       <x:c r="E29" s="1" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29" s="1" t="str">
-        <x:v>100</x:v>
-      </x:c>
+        <x:v>CT_2A_1Mid_2B</x:v>
+      </x:c>
+      <x:c r="F29" s="1"/>
+      <x:c r="G29" s="1"/>
       <x:c r="H29" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>none</x:v>
       </x:c>
       <x:c r="I29" s="1" t="str">
-        <x:v>Minimum HP.</x:v>
+        <x:v>Configured CT fallback setup.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="1"/>
       <x:c r="B30" s="1" t="str">
-        <x:v>MaxHP</x:v>
+        <x:v>StrategyRepeatWindow</x:v>
       </x:c>
       <x:c r="C30" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D30" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E30" s="1" t="str">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F30" s="1" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="1" t="str">
-        <x:v>100</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H30" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>round</x:v>
       </x:c>
       <x:c r="I30" s="1" t="str">
-        <x:v>Maximum HP.</x:v>
+        <x:v>Strategy memory window.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="1"/>
       <x:c r="B31" s="1" t="str">
-        <x:v>MinStamina</x:v>
+        <x:v>RepeatFreeCount</x:v>
       </x:c>
       <x:c r="C31" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D31" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E31" s="1" t="str">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F31" s="1" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G31" s="1" t="str">
-        <x:v>100</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H31" s="1" t="str">
-        <x:v>score</x:v>
+        <x:v>round</x:v>
       </x:c>
       <x:c r="I31" s="1" t="str">
-        <x:v>Minimum stamina.</x:v>
+        <x:v>Repeat count before penalty.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="1"/>
       <x:c r="B32" s="1" t="str">
-        <x:v>MaxStamina</x:v>
+        <x:v>StrategyRepeatPenalty</x:v>
       </x:c>
       <x:c r="C32" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D32" s="1" t="str">
-        <x:v>Int</x:v>
+        <x:v>Float</x:v>
       </x:c>
       <x:c r="E32" s="1" t="str">
-        <x:v>100</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F32" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G32" s="1" t="str">
-        <x:v>100</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="1" t="str">
         <x:v>score</x:v>
       </x:c>
       <x:c r="I32" s="1" t="str">
-        <x:v>Maximum stamina.</x:v>
+        <x:v>Repeat strategy penalty.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="1"/>
       <x:c r="B33" s="1" t="str">
-        <x:v>MinFocus</x:v>
+        <x:v>SuccessBonusPerRound</x:v>
       </x:c>
       <x:c r="C33" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D33" s="1" t="str">
-        <x:v>Int</x:v>
+        <x:v>Float</x:v>
       </x:c>
       <x:c r="E33" s="1" t="str">
-        <x:v>0</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="F33" s="1" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G33" s="1" t="str">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H33" s="1" t="str">
         <x:v>score</x:v>
       </x:c>
       <x:c r="I33" s="1" t="str">
-        <x:v>Minimum focus.</x:v>
+        <x:v>Recent success bonus.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="1"/>
       <x:c r="B34" s="1" t="str">
-        <x:v>MaxFocus</x:v>
+        <x:v>MaxPreviousSuccessBonus</x:v>
       </x:c>
       <x:c r="C34" s="1" t="str">
         <x:v>Clamp</x:v>
       </x:c>
       <x:c r="D34" s="1" t="str">
-        <x:v>Int</x:v>
+        <x:v>Float</x:v>
       </x:c>
       <x:c r="E34" s="1" t="str">
-        <x:v>100</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F34" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G34" s="1" t="str">
-        <x:v>100</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H34" s="1" t="str">
         <x:v>score</x:v>
       </x:c>
       <x:c r="I34" s="1" t="str">
-        <x:v>Maximum focus.</x:v>
+        <x:v>Maximum previous success bonus.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="1" t="str">
-        <x:v>MinHitChance</x:v>
+        <x:v>CounterMemoryBonus</x:v>
       </x:c>
       <x:c r="C35" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="D35" s="1" t="str">
         <x:v>Float</x:v>
       </x:c>
       <x:c r="E35" s="1" t="str">
-        <x:v>0.05</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F35" s="1" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G35" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H35" s="1" t="str">
-        <x:v>percent</x:v>
+        <x:v>score</x:v>
       </x:c>
       <x:c r="I35" s="1" t="str">
-        <x:v>Minimum hit chance.</x:v>
+        <x:v>Counter memory bonus.</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="1"/>
       <x:c r="B36" s="1" t="str">
-        <x:v>MaxHitChance</x:v>
+        <x:v>MinStrategyWeight</x:v>
       </x:c>
       <x:c r="C36" s="1" t="str">
         <x:v>Clamp</x:v>
@@ -1232,25 +1224,25 @@
         <x:v>Float</x:v>
       </x:c>
       <x:c r="E36" s="1" t="str">
-        <x:v>0.95</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F36" s="1" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G36" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H36" s="1" t="str">
-        <x:v>percent</x:v>
+        <x:v>score</x:v>
       </x:c>
       <x:c r="I36" s="1" t="str">
-        <x:v>Maximum hit chance.</x:v>
+        <x:v>Minimum strategy candidate weight.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="1"/>
       <x:c r="B37" s="1" t="str">
-        <x:v>MaxKillChance</x:v>
+        <x:v>MaxStrategyWeight</x:v>
       </x:c>
       <x:c r="C37" s="1" t="str">
         <x:v>Clamp</x:v>
@@ -1259,203 +1251,878 @@
         <x:v>Float</x:v>
       </x:c>
       <x:c r="E37" s="1" t="str">
-        <x:v>0.85</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F37" s="1" t="str">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G37" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H37" s="1" t="str">
-        <x:v>percent</x:v>
+        <x:v>score</x:v>
       </x:c>
       <x:c r="I37" s="1" t="str">
-        <x:v>Maximum kill chance.</x:v>
+        <x:v>Maximum strategy candidate weight.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="1"/>
       <x:c r="B38" s="1" t="str">
-        <x:v>MinPlantTime</x:v>
+        <x:v>ControlIntelTTL</x:v>
       </x:c>
       <x:c r="C38" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Intel</x:v>
       </x:c>
       <x:c r="D38" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E38" s="1" t="str">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F38" s="1" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G38" s="1" t="str">
-        <x:v>10</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H38" s="1" t="str">
         <x:v>s</x:v>
       </x:c>
       <x:c r="I38" s="1" t="str">
-        <x:v>Minimum plant time.</x:v>
+        <x:v>Control intel TTL.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="1"/>
       <x:c r="B39" s="1" t="str">
-        <x:v>MaxPlantTime</x:v>
+        <x:v>CommunicationDelay</x:v>
       </x:c>
       <x:c r="C39" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Intel</x:v>
       </x:c>
       <x:c r="D39" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E39" s="1" t="str">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F39" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G39" s="1" t="str">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="1" t="str">
         <x:v>s</x:v>
       </x:c>
       <x:c r="I39" s="1" t="str">
-        <x:v>Maximum plant time.</x:v>
+        <x:v>First-version team communication delay; must be zero.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="1"/>
       <x:c r="B40" s="1" t="str">
-        <x:v>MinDefuseTime</x:v>
+        <x:v>SoundIntelMinConfidence</x:v>
       </x:c>
       <x:c r="C40" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Intel</x:v>
       </x:c>
       <x:c r="D40" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E40" s="1" t="str">
-        <x:v>5</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F40" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G40" s="1" t="str">
-        <x:v>15</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H40" s="1" t="str">
-        <x:v>s</x:v>
+        <x:v>percent</x:v>
       </x:c>
       <x:c r="I40" s="1" t="str">
-        <x:v>Minimum defuse time.</x:v>
+        <x:v>Minimum real sound intel confidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="1"/>
       <x:c r="B41" s="1" t="str">
-        <x:v>MaxDefuseTime</x:v>
+        <x:v>SoundIntelMaxConfidence</x:v>
       </x:c>
       <x:c r="C41" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Intel</x:v>
       </x:c>
       <x:c r="D41" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E41" s="1" t="str">
-        <x:v>12</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F41" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G41" s="1" t="str">
-        <x:v>20</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H41" s="1" t="str">
-        <x:v>s</x:v>
+        <x:v>percent</x:v>
       </x:c>
       <x:c r="I41" s="1" t="str">
-        <x:v>Maximum defuse time.</x:v>
+        <x:v>Maximum real sound intel confidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="1"/>
       <x:c r="B42" s="1" t="str">
-        <x:v>MinMoveTime</x:v>
+        <x:v>DeathIntelMaxConfidence</x:v>
       </x:c>
       <x:c r="C42" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Intel</x:v>
       </x:c>
       <x:c r="D42" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E42" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F42" s="1" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G42" s="1" t="str">
-        <x:v>20</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H42" s="1" t="str">
-        <x:v>s</x:v>
+        <x:v>percent</x:v>
       </x:c>
       <x:c r="I42" s="1" t="str">
-        <x:v>Minimum move time.</x:v>
+        <x:v>Maximum death-source intel confidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="1"/>
       <x:c r="B43" s="1" t="str">
-        <x:v>MaxMoveTime</x:v>
+        <x:v>MinIntelTTL</x:v>
       </x:c>
       <x:c r="C43" s="1" t="str">
-        <x:v>Clamp</x:v>
+        <x:v>Intel</x:v>
       </x:c>
       <x:c r="D43" s="1" t="str">
         <x:v>Int</x:v>
       </x:c>
       <x:c r="E43" s="1" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="str">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F43" s="1" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="str">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="H43" s="1" t="str">
         <x:v>s</x:v>
       </x:c>
       <x:c r="I43" s="1" t="str">
-        <x:v>Maximum move time.</x:v>
+        <x:v>Minimum intel TTL.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44"/>
       <x:c r="B44" t="str">
+        <x:v>MaxIntelTTL</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>Intel</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>s</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>Maximum intel TTL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45"/>
+      <x:c r="B45" t="str">
+        <x:v>UtilityBudget</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Resource</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>Per-team round utility budget.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46"/>
+      <x:c r="B46" t="str">
+        <x:v>MaxStateTransitions</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>Maximum state transitions per round.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47"/>
+      <x:c r="B47" t="str">
+        <x:v>MaxScheduledActions</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>Maximum scheduled actions per round.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48"/>
+      <x:c r="B48" t="str">
+        <x:v>MaxEffectsPerTimestamp</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="I48" t="str">
+        <x:v>Maximum effects in one timestamp batch.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49"/>
+      <x:c r="B49" t="str">
+        <x:v>MaxNoOpTransitions</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="I49" t="str">
+        <x:v>No-op threshold before deterministic recovery.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50"/>
+      <x:c r="B50" t="str">
+        <x:v>MaxRotationsPerTeam</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F50" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G50" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H50" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="I50" t="str">
+        <x:v>Maximum proactive rotations per team.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51"/>
+      <x:c r="B51" t="str">
+        <x:v>MaxRoundTimeline</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E51" t="str">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F51" t="str">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G51" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H51" t="str">
+        <x:v>s</x:v>
+      </x:c>
+      <x:c r="I51" t="str">
+        <x:v>Maximum absolute round timeline.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52"/>
+      <x:c r="B52" t="str">
+        <x:v>MinAttribute</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D52" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E52" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F52" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G52" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H52" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="I52" t="str">
+        <x:v>Minimum attribute value.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53"/>
+      <x:c r="B53" t="str">
+        <x:v>MaxAttribute</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D53" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E53" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F53" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G53" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H53" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="I53" t="str">
+        <x:v>Maximum attribute value.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54"/>
+      <x:c r="B54" t="str">
+        <x:v>MinHP</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D54" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E54" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F54" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G54" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H54" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="I54" t="str">
+        <x:v>Minimum HP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55"/>
+      <x:c r="B55" t="str">
+        <x:v>MaxHP</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E55" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F55" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G55" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H55" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="I55" t="str">
+        <x:v>Maximum HP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56"/>
+      <x:c r="B56" t="str">
+        <x:v>MinStamina</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D56" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E56" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F56" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G56" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H56" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="I56" t="str">
+        <x:v>Minimum stamina.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57"/>
+      <x:c r="B57" t="str">
+        <x:v>MaxStamina</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D57" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E57" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F57" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G57" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H57" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="I57" t="str">
+        <x:v>Maximum stamina.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58"/>
+      <x:c r="B58" t="str">
+        <x:v>MinFocus</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D58" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E58" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F58" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G58" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H58" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="I58" t="str">
+        <x:v>Minimum focus.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59"/>
+      <x:c r="B59" t="str">
+        <x:v>MaxFocus</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D59" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E59" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F59" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G59" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H59" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="I59" t="str">
+        <x:v>Maximum focus.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60"/>
+      <x:c r="B60" t="str">
+        <x:v>MinHitChance</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D60" t="str">
+        <x:v>Float</x:v>
+      </x:c>
+      <x:c r="E60" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="F60" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G60" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H60" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="I60" t="str">
+        <x:v>Minimum hit chance.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61"/>
+      <x:c r="B61" t="str">
+        <x:v>MaxHitChance</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D61" t="str">
+        <x:v>Float</x:v>
+      </x:c>
+      <x:c r="E61" t="str">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="F61" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G61" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H61" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="I61" t="str">
+        <x:v>Maximum hit chance.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62"/>
+      <x:c r="B62" t="str">
+        <x:v>MaxKillChance</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D62" t="str">
+        <x:v>Float</x:v>
+      </x:c>
+      <x:c r="E62" t="str">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="F62" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G62" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H62" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="I62" t="str">
+        <x:v>Maximum kill chance.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63"/>
+      <x:c r="B63" t="str">
+        <x:v>MinPlantTime</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D63" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E63" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F63" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G63" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H63" t="str">
+        <x:v>s</x:v>
+      </x:c>
+      <x:c r="I63" t="str">
+        <x:v>Minimum plant time.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64"/>
+      <x:c r="B64" t="str">
+        <x:v>MaxPlantTime</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D64" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E64" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F64" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G64" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H64" t="str">
+        <x:v>s</x:v>
+      </x:c>
+      <x:c r="I64" t="str">
+        <x:v>Maximum plant time.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65"/>
+      <x:c r="B65" t="str">
+        <x:v>MinDefuseTime</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D65" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E65" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F65" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G65" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H65" t="str">
+        <x:v>s</x:v>
+      </x:c>
+      <x:c r="I65" t="str">
+        <x:v>Minimum defuse time.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66"/>
+      <x:c r="B66" t="str">
+        <x:v>MaxDefuseTime</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E66" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F66" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G66" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H66" t="str">
+        <x:v>s</x:v>
+      </x:c>
+      <x:c r="I66" t="str">
+        <x:v>Maximum defuse time.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67"/>
+      <x:c r="B67" t="str">
+        <x:v>MinMoveTime</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D67" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E67" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F67" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G67" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H67" t="str">
+        <x:v>s</x:v>
+      </x:c>
+      <x:c r="I67" t="str">
+        <x:v>Minimum move time.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68"/>
+      <x:c r="B68" t="str">
+        <x:v>MaxMoveTime</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>Clamp</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
+        <x:v>Int</x:v>
+      </x:c>
+      <x:c r="E68" t="str">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F68" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G68" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H68" t="str">
+        <x:v>s</x:v>
+      </x:c>
+      <x:c r="I68" t="str">
+        <x:v>Maximum move time.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69"/>
+      <x:c r="B69" t="str">
         <x:v>BattleReportDebugLog</x:v>
       </x:c>
-      <x:c r="C44" t="str">
+      <x:c r="C69" t="str">
         <x:v>Debug</x:v>
       </x:c>
-      <x:c r="D44" t="str">
+      <x:c r="D69" t="str">
         <x:v>Bool</x:v>
       </x:c>
-      <x:c r="E44" t="str">
+      <x:c r="E69" t="str">
         <x:v>true</x:v>
       </x:c>
-      <x:c r="F44" t="str"/>
-      <x:c r="G44" t="str"/>
-      <x:c r="H44" t="str">
+      <x:c r="F69"/>
+      <x:c r="G69"/>
+      <x:c r="H69" t="str">
         <x:v>switch</x:v>
       </x:c>
-      <x:c r="I44" t="str">
+      <x:c r="I69" t="str">
         <x:v>Enable full battle report logs in the browser console.</x:v>
       </x:c>
     </x:row>
